--- a/public/plantilla-manifiesto-rcd.xlsx
+++ b/public/plantilla-manifiesto-rcd.xlsx
@@ -15,6 +15,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="165" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <name val="Calibri"/>

--- a/public/plantilla-manifiesto-rcd.xlsx
+++ b/public/plantilla-manifiesto-rcd.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="9" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifiesto de RCD" sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-manifiesto-rcd.xlsx
+++ b/public/plantilla-manifiesto-rcd.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifiesto de RCD" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,12 +16,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="hh:mm"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -166,6 +166,10 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -532,7 +536,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -560,19 +564,19 @@
     <xf numFmtId="4" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -621,7 +625,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -639,7 +643,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -674,7 +678,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -776,6 +780,55 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="13" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1236,6 +1289,7 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="27" min="1" max="1"/>
     <col width="13" customWidth="1" style="27" min="2" max="3"/>
+    <col width="13" customWidth="1" style="27" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="27" min="4" max="4"/>
     <col width="10" customWidth="1" style="27" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="27" min="6" max="6"/>
@@ -1402,20 +1456,20 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="22" t="n"/>
+      <c r="C11" s="103" t="n"/>
+      <c r="D11" s="104" t="n"/>
+      <c r="E11" s="104" t="n"/>
+      <c r="F11" s="104" t="n"/>
+      <c r="G11" s="105" t="n"/>
       <c r="H11" s="68" t="inlineStr">
         <is>
           <t>Manifiesto N°</t>
         </is>
       </c>
       <c r="I11" s="22" t="n"/>
-      <c r="J11" s="32" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="J11" s="106" t="n"/>
+      <c r="K11" s="104" t="n"/>
+      <c r="L11" s="105" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="27">
       <c r="A12" s="68" t="inlineStr">
@@ -1424,20 +1478,20 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="22" t="n"/>
+      <c r="C12" s="103" t="n"/>
+      <c r="D12" s="104" t="n"/>
+      <c r="E12" s="104" t="n"/>
+      <c r="F12" s="104" t="n"/>
+      <c r="G12" s="105" t="n"/>
       <c r="H12" s="68" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
       <c r="I12" s="22" t="n"/>
-      <c r="J12" s="23" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="J12" s="107" t="n"/>
+      <c r="K12" s="104" t="n"/>
+      <c r="L12" s="105" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="27">
       <c r="A13" s="68" t="inlineStr">
@@ -1446,20 +1500,20 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="22" t="n"/>
+      <c r="C13" s="103" t="n"/>
+      <c r="D13" s="104" t="n"/>
+      <c r="E13" s="104" t="n"/>
+      <c r="F13" s="104" t="n"/>
+      <c r="G13" s="105" t="n"/>
       <c r="H13" s="68" t="inlineStr">
         <is>
           <t>Responsable en obra</t>
         </is>
       </c>
       <c r="I13" s="22" t="n"/>
-      <c r="J13" s="24" t="n"/>
-      <c r="K13" s="25" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="J13" s="103" t="n"/>
+      <c r="K13" s="104" t="n"/>
+      <c r="L13" s="105" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="27">
       <c r="A14" s="50" t="inlineStr">
@@ -1486,20 +1540,20 @@
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="22" t="n"/>
+      <c r="C15" s="103" t="n"/>
+      <c r="D15" s="104" t="n"/>
+      <c r="E15" s="104" t="n"/>
+      <c r="F15" s="104" t="n"/>
+      <c r="G15" s="105" t="n"/>
       <c r="H15" s="68" t="inlineStr">
         <is>
           <t>NIT</t>
         </is>
       </c>
       <c r="I15" s="22" t="n"/>
-      <c r="J15" s="24" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="22" t="n"/>
+      <c r="J15" s="103" t="n"/>
+      <c r="K15" s="104" t="n"/>
+      <c r="L15" s="105" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="27">
       <c r="A16" s="68" t="inlineStr">
@@ -1508,20 +1562,20 @@
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="22" t="n"/>
+      <c r="C16" s="103" t="n"/>
+      <c r="D16" s="104" t="n"/>
+      <c r="E16" s="104" t="n"/>
+      <c r="F16" s="104" t="n"/>
+      <c r="G16" s="105" t="n"/>
       <c r="H16" s="68" t="inlineStr">
         <is>
           <t>Cédula</t>
         </is>
       </c>
       <c r="I16" s="22" t="n"/>
-      <c r="J16" s="24" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="22" t="n"/>
+      <c r="J16" s="103" t="n"/>
+      <c r="K16" s="104" t="n"/>
+      <c r="L16" s="105" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1" s="27">
       <c r="A17" s="68" t="inlineStr">
@@ -1530,24 +1584,24 @@
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="22" t="n"/>
+      <c r="C17" s="106" t="n"/>
+      <c r="D17" s="105" t="n"/>
       <c r="E17" s="68" t="inlineStr">
         <is>
           <t>Capacidad (m³)</t>
         </is>
       </c>
       <c r="F17" s="22" t="n"/>
-      <c r="G17" s="32" t="n"/>
-      <c r="H17" s="22" t="n"/>
+      <c r="G17" s="106" t="n"/>
+      <c r="H17" s="105" t="n"/>
       <c r="I17" s="68" t="inlineStr">
         <is>
           <t>N° de autorización</t>
         </is>
       </c>
       <c r="J17" s="22" t="n"/>
-      <c r="K17" s="24" t="n"/>
-      <c r="L17" s="22" t="n"/>
+      <c r="K17" s="103" t="n"/>
+      <c r="L17" s="105" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="27">
       <c r="A18" s="50" t="inlineStr">
@@ -1568,28 +1622,28 @@
       <c r="L18" s="18" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="27">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="108" t="inlineStr">
         <is>
           <t>☐ Tierra y material de excavación</t>
         </is>
       </c>
       <c r="B19" s="17" t="n"/>
       <c r="C19" s="18" t="n"/>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="108" t="inlineStr">
         <is>
           <t>☐ Concreto y mezclas</t>
         </is>
       </c>
       <c r="E19" s="17" t="n"/>
       <c r="F19" s="18" t="n"/>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="108" t="inlineStr">
         <is>
           <t>☐ Ladrillo, bloque y cerámica</t>
         </is>
       </c>
       <c r="H19" s="17" t="n"/>
       <c r="I19" s="18" t="n"/>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J19" s="108" t="inlineStr">
         <is>
           <t>☐ Arena, grava y agregados</t>
         </is>
@@ -1598,28 +1652,28 @@
       <c r="L19" s="18" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="27">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="108" t="inlineStr">
         <is>
           <t>☐ Asfalto y material de fresado</t>
         </is>
       </c>
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="18" t="n"/>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="108" t="inlineStr">
         <is>
           <t>☐ Madera</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
       <c r="F20" s="18" t="n"/>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="108" t="inlineStr">
         <is>
           <t>☐ Metales (hierro, acero, aluminio)</t>
         </is>
       </c>
       <c r="H20" s="17" t="n"/>
       <c r="I20" s="18" t="n"/>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J20" s="108" t="inlineStr">
         <is>
           <t>☐ Vidrio</t>
         </is>
@@ -1628,28 +1682,28 @@
       <c r="L20" s="18" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="27">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="108" t="inlineStr">
         <is>
           <t>☐ Plástico</t>
         </is>
       </c>
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="18" t="n"/>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="108" t="inlineStr">
         <is>
           <t>☐ Cartón y papel</t>
         </is>
       </c>
       <c r="E21" s="17" t="n"/>
       <c r="F21" s="18" t="n"/>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="108" t="inlineStr">
         <is>
           <t>☐ Yeso, drywall y cielo raso</t>
         </is>
       </c>
       <c r="H21" s="17" t="n"/>
       <c r="I21" s="18" t="n"/>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J21" s="108" t="inlineStr">
         <is>
           <t>☐ Cables, tuberías y accesorios</t>
         </is>
@@ -1658,28 +1712,28 @@
       <c r="L21" s="18" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="27">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="108" t="inlineStr">
         <is>
           <t>☐ Tierra o material contaminado</t>
         </is>
       </c>
       <c r="B22" s="17" t="n"/>
       <c r="C22" s="18" t="n"/>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="108" t="inlineStr">
         <is>
           <t>☐ Asbesto-cemento (fibrocemento)</t>
         </is>
       </c>
       <c r="E22" s="17" t="n"/>
       <c r="F22" s="18" t="n"/>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="108" t="inlineStr">
         <is>
           <t>☐ Mezclado / sin clasificar</t>
         </is>
       </c>
       <c r="H22" s="17" t="n"/>
       <c r="I22" s="18" t="n"/>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J22" s="108" t="inlineStr">
         <is>
           <t>☐ Otro</t>
         </is>
@@ -1694,24 +1748,24 @@
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="22" t="n"/>
+      <c r="C23" s="106" t="n"/>
+      <c r="D23" s="105" t="n"/>
       <c r="E23" s="68" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
       <c r="F23" s="22" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="22" t="n"/>
+      <c r="G23" s="106" t="n"/>
+      <c r="H23" s="105" t="n"/>
       <c r="I23" s="68" t="inlineStr">
         <is>
           <t>N° de viajes</t>
         </is>
       </c>
       <c r="J23" s="22" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="22" t="n"/>
+      <c r="K23" s="106" t="n"/>
+      <c r="L23" s="105" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="27">
       <c r="A24" s="50" t="inlineStr">
@@ -1778,132 +1832,132 @@
       <c r="L25" s="21" t="n"/>
     </row>
     <row r="26" ht="19.95" customHeight="1" s="27">
-      <c r="A26" s="41" t="n">
+      <c r="A26" s="109" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="41" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="16" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="17" t="n"/>
-      <c r="L26" s="18" t="n"/>
+      <c r="B26" s="110" t="n"/>
+      <c r="C26" s="111" t="n"/>
+      <c r="D26" s="112" t="n"/>
+      <c r="E26" s="113" t="n"/>
+      <c r="F26" s="114" t="n"/>
+      <c r="G26" s="112" t="n"/>
+      <c r="H26" s="110" t="n"/>
+      <c r="I26" s="112" t="n"/>
+      <c r="J26" s="115" t="n"/>
+      <c r="K26" s="115" t="n"/>
+      <c r="L26" s="113" t="n"/>
     </row>
     <row r="27" ht="19.95" customHeight="1" s="27">
-      <c r="A27" s="41" t="n">
+      <c r="A27" s="109" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="41" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="17" t="n"/>
-      <c r="L27" s="18" t="n"/>
+      <c r="B27" s="110" t="n"/>
+      <c r="C27" s="111" t="n"/>
+      <c r="D27" s="112" t="n"/>
+      <c r="E27" s="113" t="n"/>
+      <c r="F27" s="114" t="n"/>
+      <c r="G27" s="112" t="n"/>
+      <c r="H27" s="110" t="n"/>
+      <c r="I27" s="112" t="n"/>
+      <c r="J27" s="115" t="n"/>
+      <c r="K27" s="115" t="n"/>
+      <c r="L27" s="113" t="n"/>
     </row>
     <row r="28" ht="19.95" customHeight="1" s="27">
-      <c r="A28" s="41" t="n">
+      <c r="A28" s="109" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="41" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="16" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="17" t="n"/>
-      <c r="L28" s="18" t="n"/>
+      <c r="B28" s="110" t="n"/>
+      <c r="C28" s="111" t="n"/>
+      <c r="D28" s="112" t="n"/>
+      <c r="E28" s="113" t="n"/>
+      <c r="F28" s="114" t="n"/>
+      <c r="G28" s="112" t="n"/>
+      <c r="H28" s="110" t="n"/>
+      <c r="I28" s="112" t="n"/>
+      <c r="J28" s="115" t="n"/>
+      <c r="K28" s="115" t="n"/>
+      <c r="L28" s="113" t="n"/>
     </row>
     <row r="29" ht="19.95" customHeight="1" s="27">
-      <c r="A29" s="41" t="n">
+      <c r="A29" s="109" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="41" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="16" t="n"/>
-      <c r="J29" s="17" t="n"/>
-      <c r="K29" s="17" t="n"/>
-      <c r="L29" s="18" t="n"/>
+      <c r="B29" s="110" t="n"/>
+      <c r="C29" s="111" t="n"/>
+      <c r="D29" s="112" t="n"/>
+      <c r="E29" s="113" t="n"/>
+      <c r="F29" s="114" t="n"/>
+      <c r="G29" s="112" t="n"/>
+      <c r="H29" s="110" t="n"/>
+      <c r="I29" s="112" t="n"/>
+      <c r="J29" s="115" t="n"/>
+      <c r="K29" s="115" t="n"/>
+      <c r="L29" s="113" t="n"/>
     </row>
     <row r="30" ht="19.95" customHeight="1" s="27">
-      <c r="A30" s="41" t="n">
+      <c r="A30" s="109" t="n">
         <v>5</v>
       </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="41" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="17" t="n"/>
-      <c r="L30" s="18" t="n"/>
+      <c r="B30" s="110" t="n"/>
+      <c r="C30" s="111" t="n"/>
+      <c r="D30" s="112" t="n"/>
+      <c r="E30" s="113" t="n"/>
+      <c r="F30" s="114" t="n"/>
+      <c r="G30" s="112" t="n"/>
+      <c r="H30" s="110" t="n"/>
+      <c r="I30" s="112" t="n"/>
+      <c r="J30" s="115" t="n"/>
+      <c r="K30" s="115" t="n"/>
+      <c r="L30" s="113" t="n"/>
     </row>
     <row r="31" ht="19.95" customHeight="1" s="27">
-      <c r="A31" s="41" t="n">
+      <c r="A31" s="109" t="n">
         <v>6</v>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="41" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="16" t="n"/>
-      <c r="J31" s="17" t="n"/>
-      <c r="K31" s="17" t="n"/>
-      <c r="L31" s="18" t="n"/>
+      <c r="B31" s="110" t="n"/>
+      <c r="C31" s="111" t="n"/>
+      <c r="D31" s="112" t="n"/>
+      <c r="E31" s="113" t="n"/>
+      <c r="F31" s="114" t="n"/>
+      <c r="G31" s="112" t="n"/>
+      <c r="H31" s="110" t="n"/>
+      <c r="I31" s="112" t="n"/>
+      <c r="J31" s="115" t="n"/>
+      <c r="K31" s="115" t="n"/>
+      <c r="L31" s="113" t="n"/>
     </row>
     <row r="32" ht="19.95" customHeight="1" s="27">
-      <c r="A32" s="41" t="n">
+      <c r="A32" s="109" t="n">
         <v>7</v>
       </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="41" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="16" t="n"/>
-      <c r="J32" s="17" t="n"/>
-      <c r="K32" s="17" t="n"/>
-      <c r="L32" s="18" t="n"/>
+      <c r="B32" s="110" t="n"/>
+      <c r="C32" s="111" t="n"/>
+      <c r="D32" s="112" t="n"/>
+      <c r="E32" s="113" t="n"/>
+      <c r="F32" s="114" t="n"/>
+      <c r="G32" s="112" t="n"/>
+      <c r="H32" s="110" t="n"/>
+      <c r="I32" s="112" t="n"/>
+      <c r="J32" s="115" t="n"/>
+      <c r="K32" s="115" t="n"/>
+      <c r="L32" s="113" t="n"/>
     </row>
     <row r="33" ht="19.95" customHeight="1" s="27">
-      <c r="A33" s="41" t="n">
+      <c r="A33" s="109" t="n">
         <v>8</v>
       </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="41" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="16" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="17" t="n"/>
-      <c r="K33" s="17" t="n"/>
-      <c r="L33" s="18" t="n"/>
+      <c r="B33" s="110" t="n"/>
+      <c r="C33" s="111" t="n"/>
+      <c r="D33" s="112" t="n"/>
+      <c r="E33" s="113" t="n"/>
+      <c r="F33" s="114" t="n"/>
+      <c r="G33" s="112" t="n"/>
+      <c r="H33" s="110" t="n"/>
+      <c r="I33" s="112" t="n"/>
+      <c r="J33" s="115" t="n"/>
+      <c r="K33" s="115" t="n"/>
+      <c r="L33" s="113" t="n"/>
     </row>
     <row r="34" ht="19.95" customHeight="1" s="27">
       <c r="A34" s="39" t="inlineStr">
@@ -1915,7 +1969,7 @@
       <c r="C34" s="25" t="n"/>
       <c r="D34" s="25" t="n"/>
       <c r="E34" s="22" t="n"/>
-      <c r="F34" s="61">
+      <c r="F34" s="116">
         <f>SUM(F26:F33)</f>
         <v/>
       </c>
@@ -1924,10 +1978,10 @@
         <v/>
       </c>
       <c r="H34" s="22" t="n"/>
-      <c r="I34" s="24" t="n"/>
-      <c r="J34" s="25" t="n"/>
-      <c r="K34" s="25" t="n"/>
-      <c r="L34" s="22" t="n"/>
+      <c r="I34" s="103" t="n"/>
+      <c r="J34" s="104" t="n"/>
+      <c r="K34" s="104" t="n"/>
+      <c r="L34" s="105" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="27">
       <c r="A35" s="50" t="inlineStr">
@@ -1954,20 +2008,20 @@
         </is>
       </c>
       <c r="B36" s="22" t="n"/>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="25" t="n"/>
-      <c r="E36" s="25" t="n"/>
-      <c r="F36" s="25" t="n"/>
-      <c r="G36" s="22" t="n"/>
+      <c r="C36" s="103" t="n"/>
+      <c r="D36" s="104" t="n"/>
+      <c r="E36" s="104" t="n"/>
+      <c r="F36" s="104" t="n"/>
+      <c r="G36" s="105" t="n"/>
       <c r="H36" s="68" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
       <c r="I36" s="22" t="n"/>
-      <c r="J36" s="24" t="n"/>
-      <c r="K36" s="25" t="n"/>
-      <c r="L36" s="22" t="n"/>
+      <c r="J36" s="103" t="n"/>
+      <c r="K36" s="104" t="n"/>
+      <c r="L36" s="105" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1" s="27">
       <c r="A37" s="68" t="inlineStr">
@@ -1976,20 +2030,20 @@
         </is>
       </c>
       <c r="B37" s="22" t="n"/>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="25" t="n"/>
-      <c r="E37" s="25" t="n"/>
-      <c r="F37" s="25" t="n"/>
-      <c r="G37" s="22" t="n"/>
+      <c r="C37" s="103" t="n"/>
+      <c r="D37" s="104" t="n"/>
+      <c r="E37" s="104" t="n"/>
+      <c r="F37" s="104" t="n"/>
+      <c r="G37" s="105" t="n"/>
       <c r="H37" s="68" t="inlineStr">
         <is>
           <t>N° de certificado</t>
         </is>
       </c>
       <c r="I37" s="22" t="n"/>
-      <c r="J37" s="24" t="n"/>
-      <c r="K37" s="25" t="n"/>
-      <c r="L37" s="22" t="n"/>
+      <c r="J37" s="103" t="n"/>
+      <c r="K37" s="104" t="n"/>
+      <c r="L37" s="105" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1" s="27">
       <c r="A38" s="68" t="inlineStr">
@@ -1998,20 +2052,20 @@
         </is>
       </c>
       <c r="B38" s="22" t="n"/>
-      <c r="C38" s="24" t="n"/>
-      <c r="D38" s="25" t="n"/>
-      <c r="E38" s="25" t="n"/>
-      <c r="F38" s="25" t="n"/>
-      <c r="G38" s="22" t="n"/>
+      <c r="C38" s="103" t="n"/>
+      <c r="D38" s="104" t="n"/>
+      <c r="E38" s="104" t="n"/>
+      <c r="F38" s="104" t="n"/>
+      <c r="G38" s="105" t="n"/>
       <c r="H38" s="68" t="inlineStr">
         <is>
           <t>Fecha del certificado</t>
         </is>
       </c>
       <c r="I38" s="22" t="n"/>
-      <c r="J38" s="23" t="n"/>
-      <c r="K38" s="25" t="n"/>
-      <c r="L38" s="22" t="n"/>
+      <c r="J38" s="107" t="n"/>
+      <c r="K38" s="104" t="n"/>
+      <c r="L38" s="105" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="27">
       <c r="A39" s="50" t="inlineStr">
@@ -2064,24 +2118,24 @@
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="18" t="n"/>
+      <c r="C41" s="112" t="n"/>
+      <c r="D41" s="113" t="n"/>
       <c r="E41" s="72" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F41" s="18" t="n"/>
-      <c r="G41" s="19" t="n"/>
-      <c r="H41" s="18" t="n"/>
+      <c r="G41" s="112" t="n"/>
+      <c r="H41" s="113" t="n"/>
       <c r="I41" s="72" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J41" s="18" t="n"/>
-      <c r="K41" s="19" t="n"/>
-      <c r="L41" s="18" t="n"/>
+      <c r="K41" s="112" t="n"/>
+      <c r="L41" s="113" t="n"/>
     </row>
     <row r="42" ht="21" customHeight="1" s="27">
       <c r="A42" s="72" t="inlineStr">
@@ -2090,24 +2144,24 @@
         </is>
       </c>
       <c r="B42" s="18" t="n"/>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="18" t="n"/>
+      <c r="C42" s="112" t="n"/>
+      <c r="D42" s="113" t="n"/>
       <c r="E42" s="72" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F42" s="18" t="n"/>
-      <c r="G42" s="19" t="n"/>
-      <c r="H42" s="18" t="n"/>
+      <c r="G42" s="112" t="n"/>
+      <c r="H42" s="113" t="n"/>
       <c r="I42" s="72" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J42" s="18" t="n"/>
-      <c r="K42" s="19" t="n"/>
-      <c r="L42" s="18" t="n"/>
+      <c r="K42" s="112" t="n"/>
+      <c r="L42" s="113" t="n"/>
     </row>
     <row r="43" ht="21" customHeight="1" s="27">
       <c r="A43" s="72" t="inlineStr">
@@ -2116,24 +2170,24 @@
         </is>
       </c>
       <c r="B43" s="18" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="18" t="n"/>
+      <c r="C43" s="112" t="n"/>
+      <c r="D43" s="113" t="n"/>
       <c r="E43" s="72" t="inlineStr">
         <is>
           <t>Cédula:</t>
         </is>
       </c>
       <c r="F43" s="18" t="n"/>
-      <c r="G43" s="19" t="n"/>
-      <c r="H43" s="18" t="n"/>
+      <c r="G43" s="112" t="n"/>
+      <c r="H43" s="113" t="n"/>
       <c r="I43" s="72" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J43" s="18" t="n"/>
-      <c r="K43" s="19" t="n"/>
-      <c r="L43" s="18" t="n"/>
+      <c r="K43" s="112" t="n"/>
+      <c r="L43" s="113" t="n"/>
     </row>
     <row r="44" s="27">
       <c r="A44" s="1" t="inlineStr">
@@ -2147,6 +2201,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="119">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E23:F23"/>
